--- a/资源/数据/新闻/news_library_with_images.xlsx
+++ b/资源/数据/新闻/news_library_with_images.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,55 +449,60 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>摘要</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>正文</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>现象总结</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>趋势预测</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>正文末尾提示</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>默认方向</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>可选方向</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>默认强度</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>可选强度</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>反向逻辑说明</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>底层接口参数</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -536,55 +541,60 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>首脑辞职冲击市场，避险急剧升温</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>{time_text}，{region}政坛突发变动，交易席位开始担心政策连续性和后续权力交接节奏。当前价格未必一步到位，但风险资金通常会先行收缩，相关货币短线更容易陷入被动。 若官方迟迟不表态稳定市场，相关货币大概率维持偏弱震荡；若继任安排清晰，跌势也可能很快放缓。 市场接下来要看避险情绪有没有继续扩散，以及短线买盘是不是已经明显回流。</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>{time_text}，{region}政坛突发变动，交易席位开始担心政策连续性和后续权力交接节奏。当前价格未必一步到位，但风险资金通常会先行收缩，相关货币短线更容易陷入被动。</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>若官方迟迟不表态稳定市场，相关货币大概率维持偏弱震荡；若继任安排清晰，跌势也可能很快放缓。</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>市场接下来要看避险情绪有没有继续扩散，以及短线买盘是不是已经明显回流。</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>偏弱</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>偏弱|承压|震荡</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>明显</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>普通|明显|剧烈</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>若继任安排超预期稳定，或市场提前释放过恐慌，短线也可能从承压转向震荡修复。</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>sentiment_down|volatility_up</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>首相辞职|政治冲击|避险</t>
         </is>
@@ -623,55 +633,60 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>会晤无实质进展，避险情绪卷土重来</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>{time_text}，{region}高层会晤没有释放足够的缓和信号，市场对后续关系修复速度保持谨慎。价格层面未必马上剧烈失衡，但短线风险偏好通常会先收缩。 若后续沟通仍缺少实质进展，防御型货币更容易受到追捧；若很快补出安抚表态，避险交易也可能迅速降温。 这类消息接下来要看风险情绪是不是真的在发酵，以及避险买盘会不会从试探变成持续流入。</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>{time_text}，{region}高层会晤没有释放足够的缓和信号，市场对后续关系修复速度保持谨慎。价格层面未必马上剧烈失衡，但短线风险偏好通常会先收缩。</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>若后续沟通仍缺少实质进展，防御型货币更容易受到追捧；若很快补出安抚表态，避险交易也可能迅速降温。</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>这类消息接下来要看风险情绪是不是真的在发酵，以及避险买盘会不会从试探变成持续流入。</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>承压</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>承压|震荡|降温</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>若后续立刻出现缓和信号，市场可能把事件当成短暂噪音，避险需求会很快降温。</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>sentiment_down_small|safe_haven_up_small</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>高层会晤|地缘紧张|避险回流</t>
         </is>
@@ -710,55 +725,60 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>关税升级冲击贸易预期，外向货币承压</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>{time_text}，{region}释放更强硬的贸易信号，市场开始重新评估出口前景和企业利润。相关货币短期内可能先走分化——外向依赖度更高的一侧更容易先承压。 若后续出现反制措施或谈判受阻，贸易相关货币可能继续反复走弱；若双方措辞回温，市场也可能很快转回观望。 交易员通常会盯住出口预期有没有恶化，以及市场风险偏好是不是还在往下走。</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>{time_text}，{region}释放更强硬的贸易信号，市场开始重新评估出口前景和企业利润。相关货币短期内可能先走分化——外向依赖度更高的一侧更容易先承压。</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>若后续出现反制措施或谈判受阻，贸易相关货币可能继续反复走弱；若双方措辞回温，市场也可能很快转回观望。</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>交易员通常会盯住出口预期有没有恶化，以及市场风险偏好是不是还在往下走。</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>偏弱</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>偏弱|分化|承压</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>明显</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>普通|明显|剧烈</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>若市场同步押注谈判回补或替代出口受益，局部货币也可能出现分化甚至短线修复。</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>trade_bias_shift|sentiment_down|safe_haven_up</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>关税|贸易战|出口预期</t>
         </is>
@@ -797,55 +817,60 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>航运仓储成本攀升，出口兑现效率承压</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>{time_text}，航运排期与仓储成本出现同步波动，市场开始担心{region}部分出口链条的兑现效率。汇率未必立刻失速，但中期支持力量显得没有此前稳定。 若物流与订单双双走弱，相关货币可能逐步转入温和承压；若供应链恢复顺畅，市场会把这次扰动视作阶段性噪音。 贸易类消息接下来更值得盯的，是外部订单有没有继续走软，以及支撑汇率的那个出口优势是不是在被慢慢削弱。</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>{time_text}，航运排期与仓储成本出现同步波动，市场开始担心{region}部分出口链条的兑现效率。汇率未必立刻失速，但中期支持力量显得没有此前稳定。</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>若物流与订单双双走弱，相关货币可能逐步转入温和承压；若供应链恢复顺畅，市场会把这次扰动视作阶段性噪音。</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>贸易类消息接下来更值得盯的，是外部订单有没有继续走软，以及支撑汇率的那个出口优势是不是在被慢慢削弱。</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>承压</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>承压|偏弱|震荡</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>若市场认为只是短期物流扰动，且外需本身未坏，汇率可能只表现为震荡而非持续走弱。</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>trade_bias_down_small|expectation_shift</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>航运|供应链|出口扰动</t>
         </is>
@@ -884,55 +909,60 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>央行口风转鹰，市场下调宽松预期</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>{time_text}，{region}央行措辞较前期更偏强硬，交易席位普遍开始下调短期宽松预期。汇率不一定立刻单边加速，但只要政策口风维持住，相关货币通常更容易得到支撑。 若后续数据继续配合强势口径，相关货币有望延续偏强节奏；若经济数据迅速转弱，当前判断也可能被市场推翻。 市场此时最关注的，是利率差距带来的支撑能不能继续维持，以及官方口风会不会重新转软。</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>{time_text}，{region}央行措辞较前期更偏强硬，交易席位普遍开始下调短期宽松预期。汇率不一定立刻单边加速，但只要政策口风维持住，相关货币通常更容易得到支撑。</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>若后续数据继续配合强势口径，相关货币有望延续偏强节奏；若经济数据迅速转弱，当前判断也可能被市场推翻。</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>市场此时最关注的，是利率差距带来的支撑能不能继续维持，以及官方口风会不会重新转软。</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>偏强</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>偏强|走稳|震荡</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>明显</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>普通|明显|剧烈</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>若市场已提前计价，或强硬口风反而加重经济担忧，方向也可能从偏强转成震荡甚至承压。</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>rate_diff_shift|expectation_up</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>央行|加息|利率路径</t>
         </is>
@@ -971,55 +1001,60 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>官方表态稳汇率，投机追击速度放缓</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>{time_text}，{region}释放更明确的稳汇率态度，市场判断官方不希望价格继续失控波动。即便趋势未被彻底改写，投机资金通常也会先降低追击速度。 若后续表态持续统一，相关货币短线波动可能逐步收敛；若市场测试压力重新抬头，这类稳定信号也可能很快被重新定价。 这类政策消息最该观察的，是市场恐慌有没有降温，以及短线波动是否真的被压回更可控的区间。</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>{time_text}，{region}释放更明确的稳汇率态度，市场判断官方不希望价格继续失控波动。即便趋势未被彻底改写，投机资金通常也会先降低追击速度。</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>若后续表态持续统一，相关货币短线波动可能逐步收敛；若市场测试压力重新抬头，这类稳定信号也可能很快被重新定价。</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>这类政策消息最该观察的，是市场恐慌有没有降温，以及短线波动是否真的被压回更可控的区间。</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>收敛</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>收敛|走稳|震荡</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>若市场把表态理解成被动防守，反而可能测试更大波动，方向会从收敛转成反复拉扯。</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>volatility_down_small|policy_signal</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>稳定汇市|口头干预|政策安抚</t>
         </is>
@@ -1058,55 +1093,60 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>数据强弱不一，市场对中期增长信心松动</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>{time_text}，{region}公布的新一轮数据强弱不一，部分机构开始下调对后续增长节奏的乐观看法。当前汇率未必立刻脱离原有区间，但市场对中期基本面的评估已经出现松动。 若接下来几轮数据继续走弱，相关货币更容易慢慢转入承压；若只是单次失真，市场也可能很快回到原判断。 交易席位接下来要看经济基本面有没有稳住，以及市场对合理价格水平的判断是不是在下移。</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>{time_text}，{region}公布的新一轮数据强弱不一，部分机构开始下调对后续增长节奏的乐观看法。当前汇率未必立刻脱离原有区间，但市场对中期基本面的评估已经出现松动。</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>若接下来几轮数据继续走弱，相关货币更容易慢慢转入承压；若只是单次失真，市场也可能很快回到原判断。</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>交易席位接下来要看经济基本面有没有稳住，以及市场对合理价格水平的判断是不是在下移。</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>承压</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>承压|震荡|分化</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>若市场原本预期更差，数据虽弱但没坏透，方向也可能从承压转成企稳或震荡。</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>expectation_shift|fair_value_drift</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>CPI|就业|增长</t>
         </is>
@@ -1145,55 +1185,60 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>通胀回落不及预期，政策宽松空间收窄</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>{time_text}，{region}最新价格数据没有像市场预想的那样顺畅回落，交易席位开始担心宽松节奏会被迫延后。汇率未必立刻脱离区间，但支撑逻辑已经变得更偏向强势一侧。 若后续通胀仍旧顽固，相关货币更容易保持韧性；若下轮数据明显降温，这种偏强判断也可能迅速被收回。 通胀类新闻接下来要看的是，价格压力会不会让政策调整的余地变小，以及市场对利率的判断是不是还在往上抬。</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>{time_text}，{region}最新价格数据没有像市场预想的那样顺畅回落，交易席位开始担心宽松节奏会被迫延后。汇率未必立刻脱离区间，但支撑逻辑已经变得更偏向强势一侧。</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>若后续通胀仍旧顽固，相关货币更容易保持韧性；若下轮数据明显降温，这种偏强判断也可能迅速被收回。</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>通胀类新闻接下来要看的是，价格压力会不会让政策调整的余地变小，以及市场对利率的判断是不是还在往上抬。</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>偏强</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>偏强|走稳|震荡</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>若市场把高通胀解读成增长受压或政策失衡，方向也可能从偏强转成震荡甚至承压。</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>rate_diff_shift|expectation_up|fair_value_drift</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>通胀|政策余地|利率重估</t>
         </is>
@@ -1232,55 +1277,60 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>机构集体转向乐观，市场风向悄然改变</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>{time_text}，多家机构报告开始转向更积极的表述，认为{region}货币此前的下行压力可能暂时缓和。价格未必已经转势，但市场风向一旦偏向同一侧，短线押注往往会先把波动带起来。 若后续消息继续配合，相关货币有机会逐步走稳；若新增利空突然出现，这类乐观判断也常常会被快速修正。 这类资讯重点不在事实本身，而在市场情绪有没有持续转暖、押注方向是否越来越一致。</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>{time_text}，多家机构报告开始转向更积极的表述，认为{region}货币此前的下行压力可能暂时缓和。价格未必已经转势，但市场风向一旦偏向同一侧，短线押注往往会先把波动带起来。</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>若后续消息继续配合，相关货币有机会逐步走稳；若新增利空突然出现，这类乐观判断也常常会被快速修正。</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>这类资讯重点不在事实本身，而在市场情绪有没有持续转暖、押注方向是否越来越一致。</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>走稳</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>走稳|偏强|回暖</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>若新增催化跟不上，或市场担心乐观过度，方向也可能从走稳转成高位反复。</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>expectation_up|sentiment_up</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>机构观点|预期转向|风向变化</t>
         </is>
@@ -1319,55 +1369,60 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>新增买盘后继乏力，追价热情明显消退</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>{time_text}，部分机构开始提醒{region}货币此前的强势已经被市场消化得差不多，新增买盘显得比前一阶段保守。价格并未失控回落，但继续上冲的动能看起来没有那么顺畅。 若后续数据和消息都难再提供催化，相关货币更可能进入高位反复；若新的利好重新出现，市场也可能再次追价。 预期类资讯此时最该看的，不是旧故事有多强，而是新增信心有没有明显减弱。</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>{time_text}，部分机构开始提醒{region}货币此前的强势已经被市场消化得差不多，新增买盘显得比前一阶段保守。价格并未失控回落，但继续上冲的动能看起来没有那么顺畅。</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>若后续数据和消息都难再提供催化，相关货币更可能进入高位反复；若新的利好重新出现，市场也可能再次追价。</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>预期类资讯此时最该看的，不是旧故事有多强，而是新增信心有没有明显减弱。</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>震荡</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>震荡|回吐|分化</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>若市场很快补出新催化，追价情绪也可能重新回暖，方向会从震荡转回走稳或偏强。</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>expectation_down_small|sentiment_down_small</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>追价降温|预期钝化|高位震荡</t>
         </is>
@@ -1406,55 +1461,60 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>多空资金激烈博弈，盘中波动急剧放大</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>{time_text}，盘面突然放量，交易员提到短线止损与追价资金同时出现。走势看上去很激烈，但这类异动未必代表中期方向已经确认，更可能只是情绪在短时间内集中释放。 若后续资金继续追着同一方向打，波动可能进一步放大；若买卖盘很快回归平衡，这次异动也可能只是一次脉冲。 盘面类新闻更该关注波动有没有继续扩散，以及市场流动性是否明显变紧。</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>{time_text}，盘面突然放量，交易员提到短线止损与追价资金同时出现。走势看上去很激烈，但这类异动未必代表中期方向已经确认，更可能只是情绪在短时间内集中释放。</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>若后续资金继续追着同一方向打，波动可能进一步放大；若买卖盘很快回归平衡，这次异动也可能只是一次脉冲。</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>盘面类新闻更该关注波动有没有继续扩散，以及市场流动性是否明显变紧。</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>放大</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>放大|拉锯|震荡</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>明显</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>普通|明显|剧烈</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>若追价和止损很快出清，方向也可能从放大转成快速收敛。</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>volatility_spike|liquidity_tighten</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>跳水|急拉|止损盘</t>
         </is>
@@ -1493,55 +1553,60 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>挂单厚度骤降，价格瞬间偏离平衡位</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>{time_text}，盘中挂单厚度明显变薄，几笔集中成交就把价格推离了原先的平衡位置。这样的行情未必代表基本面立刻生变，但会让短线交易难度明显抬高。 若流动性迟迟恢复不过来，后续价格仍可能继续放大摆动；若更大规模的对手盘及时出现，异动也可能很快被修正。 这种盘面消息要盯的重点，是市场深度有没有恢复，以及短线波动会不会持续超出平常节奏。</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>{time_text}，盘中挂单厚度明显变薄，几笔集中成交就把价格推离了原先的平衡位置。这样的行情未必代表基本面立刻生变，但会让短线交易难度明显抬高。</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>若流动性迟迟恢复不过来，后续价格仍可能继续放大摆动；若更大规模的对手盘及时出现，异动也可能很快被修正。</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>这种盘面消息要盯的重点，是市场深度有没有恢复，以及短线波动会不会持续超出平常节奏。</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>偏移</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>偏移|放大|拉锯</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>明显</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>普通|明显|剧烈</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>若对手盘很快补位，短线偏移可能迅速被修正，方向会从放大改成拉锯或收敛。</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>liquidity_tighten|volatility_up_small</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>挂单变薄|流动性收紧|快速偏移</t>
         </is>
@@ -1580,55 +1645,60 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>议息落地市场重估利率路径，短线调整开启</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>{time_text}，{region}最新议息结果出炉，市场迅速开始重新评估后续利率走向。汇率短线可能出现一轮快速调整，但更关键的是接下来的官员口风会不会延续当前信号。 若会议传递出更清晰的政策方向，相关货币容易走出单边试探；若信号模棱两可，盘面可能继续反复拉扯。 议息落地后重点要看市场对下一步利率的判断是变得更一致还是更加分歧。</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>{time_text}，{region}最新议息结果出炉，市场迅速开始重新评估后续利率走向。汇率短线可能出现一轮快速调整，但更关键的是接下来的官员口风会不会延续当前信号。</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>若会议传递出更清晰的政策方向，相关货币容易走出单边试探；若信号模棱两可，盘面可能继续反复拉扯。</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>议息落地后重点要看市场对下一步利率的判断是变得更一致还是更加分歧。</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>震荡</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>震荡|偏强|偏弱</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>若会议结果完全符合预期且无新增信号，市场可能迅速消化，方向停留在震荡而非突破。</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>rate_diff_shift|expectation_recalibrate</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>议息落地|利率预期|会后调整</t>
         </is>
@@ -1667,55 +1737,60 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>央行内部鹰鸽分化，利率预期陷入拉锯</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>{time_text}，{region}央行高层近期表态出现明显温差——有人偏向继续收紧，有人开始提示经济风险。市场暂时找不到统一参照，短线更容易在预期拉锯中来回摆动。 若鹰派声音继续占上风，相关货币可能重新获得支撑；若鸽派阵营扩大，市场会更快转向宽松押注。 官员分歧类消息最重要的是看谁的声音更有后续动作支撑，以及市场的定价偏向哪一侧。</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>{time_text}，{region}央行高层近期表态出现明显温差——有人偏向继续收紧，有人开始提示经济风险。市场暂时找不到统一参照，短线更容易在预期拉锯中来回摆动。</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>若鹰派声音继续占上风，相关货币可能重新获得支撑；若鸽派阵营扩大，市场会更快转向宽松押注。</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>官员分歧类消息最重要的是看谁的声音更有后续动作支撑，以及市场的定价偏向哪一侧。</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>震荡</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>震荡|分化|走稳</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>若后续官员表态快速统一，分歧状态可能迅速转为一致押注，方向从震荡转成偏强或偏弱。</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>policy_split|expectation_hold</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>官员分歧|鹰鸽分化|政策预期</t>
         </is>
@@ -1754,55 +1829,60 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>消息面缺乏指引，多空双方均选择观望</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>{time_text}，最新消息面缺乏明确指引，交易席位的方向判断十分分散。相关货币的成交量明显收缩，价格在相对狭窄的区间里来回试探——多数人在等下一个能打破僵局的信号。 若新增消息打破当前僵局，汇率可能迅速朝突破方向移动一小段；若持续无催化，盘面可能继续维持这种低波动观望状态。 这种时候最该看的不是价格本身，而是有没有新的催化把市场从观望中拽出来。</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>{time_text}，最新消息面缺乏明确指引，交易席位的方向判断十分分散。相关货币的成交量明显收缩，价格在相对狭窄的区间里来回试探——多数人在等下一个能打破僵局的信号。</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>若新增消息打破当前僵局，汇率可能迅速朝突破方向移动一小段；若持续无催化，盘面可能继续维持这种低波动观望状态。</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>这种时候最该看的不是价格本身，而是有没有新的催化把市场从观望中拽出来。</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>等待</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>等待|震荡|收敛</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>轻微</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>轻微|普通</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>若突发放量或重要数据出现，观望状态会被迅速打破，方向取决于消息本身。</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>expectation_hold|volatility_hold</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>观望加重|等待催化|缩量</t>
         </is>
@@ -1841,55 +1921,60 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>资金集体涌向同一方向，拥挤风险正在积累</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>{time_text}，几乎同一时间多家机构调高了对{region}货币的评价，追价资金快速涌向同一方向。这种局面短期能推动价格继续朝押注方向移动，但押注越拥挤，反转的风险也在悄悄积累。 若后续消息持续配合，一致押注可能继续推动走势；但一旦市场发现追过了头，反向修正也会来得很快。 一致押注最大的风险不是方向错了，而是方向对了但已经没有足够的人接力。</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>{time_text}，几乎同一时间多家机构调高了对{region}货币的评价，追价资金快速涌向同一方向。这种局面短期能推动价格继续朝押注方向移动，但押注越拥挤，反转的风险也在悄悄积累。</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>若后续消息持续配合，一致押注可能继续推动走势；但一旦市场发现追过了头，反向修正也会来得很快。</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>一致押注最大的风险不是方向错了，而是方向对了但已经没有足够的人接力。</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>偏强</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>偏强|回暖|走稳</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>明显</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>普通|明显|剧烈</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>若押注过于拥挤导致反转信号触发，方向可能从偏强快速转成回吐甚至踩踏。</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>sentiment_up|expectation_up</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>一致押注|拥挤交易|资金集中</t>
         </is>
@@ -1928,55 +2013,60 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>价格快速偏离后反向回摆，多空重新试探方向</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>{time_text}，价格在经历一轮快速偏移后开始出现反向回摆，部分短线获利资金选择离场，也有新资金趁机反向进场。这类修正更多是盘面的自我调整，不一定意味着原来的方向已经被推翻。 若修正力度温和、量能不大，原方向调整后可能继续延续；若修正放量且幅度很深，市场可能正在酝酿方向切换。 技术性修正的关键指标是修正过程中有没有新的大资金介入——有则可能转向，无则只是短暂歇脚。</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>{time_text}，价格在经历一轮快速偏移后开始出现反向回摆，部分短线获利资金选择离场，也有新资金趁机反向进场。这类修正更多是盘面的自我调整，不一定意味着原来的方向已经被推翻。</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>若修正力度温和、量能不大，原方向调整后可能继续延续；若修正放量且幅度很深，市场可能正在酝酿方向切换。</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>技术性修正的关键指标是修正过程中有没有新的大资金介入——有则可能转向，无则只是短暂歇脚。</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>修复</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>修复|震荡|偏移</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>若修正只是昙花一现且资金继续追原方向，盘面可能很快恢复前期偏移状态。</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>volatility_spike|liquidity_tighten</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>技术性修正|获利了结|方向试探</t>
         </is>
@@ -2015,55 +2105,60 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>紧张局势降温，避险资金开始撤退</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>{time_text}，此前持续发酵的紧张局势出现松动迹象，市场对冲突扩大的担忧明显下降。资金开始从防御型资产回流，相关货币的压力也有所减轻。不过市场仍然保持一定警惕——局势反复已经不是第一次了。 若缓和信号继续兑现，避险资金可能进一步撤退，相关货币逐步企稳；若局势再度生变，避险回流也会很快恢复。 避险退潮行情的关键在于局势是否真的在降温，而不是只是口头上的让步。</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>{time_text}，此前持续发酵的紧张局势出现松动迹象，市场对冲突扩大的担忧明显下降。资金开始从防御型资产回流，相关货币的压力也有所减轻。不过市场仍然保持一定警惕——局势反复已经不是第一次了。</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>若缓和信号继续兑现，避险资金可能进一步撤退，相关货币逐步企稳；若局势再度生变，避险回流也会很快恢复。</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>避险退潮行情的关键在于局势是否真的在降温，而不是只是口头上的让步。</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>回暖</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>回暖|修复|走稳</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>若市场认为缓和只是暂时姿态，避险需求可能只是阶段性收缩而非真正退潮。</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>sentiment_up_small|safe_haven_down_small</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>局势缓和|避险退潮|风险偏好回升</t>
         </is>
@@ -2102,55 +2197,60 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>产业链外迁苗头出现，制造业优势面临考验</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>{time_text}，部分跨国企业开始调整区域布局，降低对{region}单一生产基地的依赖。市场开始重新评估{region}制造业的长期竞争力和出口潜力。汇率不会因为一条消息就迅速变脸，但这类结构调整往往需要被认真对待。 若转移趋势加快，相关货币的中期支撑会逐步削弱；若企业重新留驻或订单回流，这种担忧也会慢慢缓解。 产业链调整的影响不是一天两天能看到的，但资金会先走——市场一旦开始计价，方向就会慢慢形成。</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>{time_text}，部分跨国企业开始调整区域布局，降低对{region}单一生产基地的依赖。市场开始重新评估{region}制造业的长期竞争力和出口潜力。汇率不会因为一条消息就迅速变脸，但这类结构调整往往需要被认真对待。</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>若转移趋势加快，相关货币的中期支撑会逐步削弱；若企业重新留驻或订单回流，这种担忧也会慢慢缓解。</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>产业链调整的影响不是一天两天能看到的，但资金会先走——市场一旦开始计价，方向就会慢慢形成。</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>偏弱</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>偏弱|承压|震荡</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>若转移被证实是小范围现象而非趋势，市场可能把它视作噪音，方向停留在震荡。</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>trade_bias_down_small|fair_value_drift</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>产业链转移|制造业|结构调整</t>
         </is>
@@ -2189,55 +2289,60 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>商品价格大幅起落，出口收入稳定性受疑</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>{time_text}，能源与资源类商品近期大幅起落，市场对{region}出口收入稳定性的信任有所动摇。这种行情对汇率的影响通常不是直线的——涨了未必全部利好，跌了也不代表基本面立刻崩溃。 若商品价格继续大幅摆动，相关货币可能进入反复拉锯；若价格趋势逐渐明朗，市场也会重新找到方向。 商品报价波动大的时候，市场更关心的是这轮波动有没有基本面支撑，还是只是资金在炒作。</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>{time_text}，能源与资源类商品近期大幅起落，市场对{region}出口收入稳定性的信任有所动摇。这种行情对汇率的影响通常不是直线的——涨了未必全部利好，跌了也不代表基本面立刻崩溃。</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>若商品价格继续大幅摆动，相关货币可能进入反复拉锯；若价格趋势逐渐明朗，市场也会重新找到方向。</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>商品报价波动大的时候，市场更关心的是这轮波动有没有基本面支撑，还是只是资金在炒作。</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>震荡</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>震荡|偏强|承压</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>若商品剧烈波动后迅速回稳，市场也可能把它当成短期噪音来处理。</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>trade_bias_shift|commodity_volatility</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>大宗商品|价格波动|出口收入</t>
         </is>
@@ -2276,55 +2381,60 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>尾盘大单集中进场，短线方向突然逆转</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>{time_text}，临近收市时盘面突然放量，价格在短时间内走出明显方向。这类尾盘异动往往来自大单集中成交或止损集中触发，不一定是全天走势的延续，但短线赌性会被放大。 若异动方向与盘中趋势一致，后续惯性可能延续；若尾盘方向与全天相反，次日开盘往往会出现修正或延续激烈博弈。 尾盘异动最需要确认的是有没有消息配合——有消息可能是方向切换的开始，没消息可能只是大单调度。</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>{time_text}，临近收市时盘面突然放量，价格在短时间内走出明显方向。这类尾盘异动往往来自大单集中成交或止损集中触发，不一定是全天走势的延续，但短线赌性会被放大。</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>若异动方向与盘中趋势一致，后续惯性可能延续；若尾盘方向与全天相反，次日开盘往往会出现修正或延续激烈博弈。</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>尾盘异动最需要确认的是有没有消息配合——有消息可能是方向切换的开始，没消息可能只是大单调度。</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>放大</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>放大|偏移|拉锯</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>明显</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>普通|明显|剧烈</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>若尾盘异动被次日的修复行情消化，方向可能只是脉冲而非真正突破。</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>volatility_spike|liquidity_tighten</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>尾盘异动|放量转向|大单成交</t>
         </is>
